--- a/Team-Data/2011-12/3-3-2011-12.xlsx
+++ b/Team-Data/2011-12/3-3-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,37 +728,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
         <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>0.595</v>
+        <v>0.583</v>
       </c>
       <c r="H2" t="n">
         <v>48.8</v>
       </c>
       <c r="I2" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J2" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.438</v>
       </c>
       <c r="L2" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M2" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.375</v>
+        <v>0.372</v>
       </c>
       <c r="O2" t="n">
         <v>15</v>
@@ -700,16 +767,16 @@
         <v>20.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.718</v>
+        <v>0.719</v>
       </c>
       <c r="R2" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S2" t="n">
         <v>31.6</v>
       </c>
       <c r="T2" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U2" t="n">
         <v>21.6</v>
@@ -721,34 +788,34 @@
         <v>8.1</v>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -757,10 +824,10 @@
         <v>18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -775,7 +842,7 @@
         <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ2" t="n">
         <v>27</v>
@@ -784,37 +851,37 @@
         <v>24</v>
       </c>
       <c r="AS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW2" t="n">
         <v>12</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>13</v>
       </c>
       <c r="AX2" t="n">
         <v>18</v>
       </c>
       <c r="AY2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>23</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -921,10 +988,10 @@
         <v>1.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF3" t="n">
         <v>14</v>
@@ -948,7 +1015,7 @@
         <v>20</v>
       </c>
       <c r="AM3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN3" t="n">
         <v>7</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -981,10 +1048,10 @@
         <v>28</v>
       </c>
       <c r="AX3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-14.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1139,7 +1206,7 @@
         <v>27</v>
       </c>
       <c r="AP4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ4" t="n">
         <v>26</v>
@@ -1157,13 +1224,13 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>25</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -1291,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
         <v>29</v>
@@ -1348,7 +1415,7 @@
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
         <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>0.371</v>
+        <v>0.382</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1407,13 +1474,13 @@
         <v>34.5</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M6" t="n">
         <v>19.4</v>
@@ -1428,19 +1495,19 @@
         <v>25.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.694</v>
+        <v>0.696</v>
       </c>
       <c r="R6" t="n">
         <v>13.1</v>
       </c>
       <c r="S6" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T6" t="n">
         <v>43.3</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V6" t="n">
         <v>15.8</v>
@@ -1452,22 +1519,22 @@
         <v>4.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-4.4</v>
+        <v>-4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>23</v>
@@ -1482,10 +1549,10 @@
         <v>13</v>
       </c>
       <c r="AI6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK6" t="n">
         <v>26</v>
@@ -1512,19 +1579,19 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV6" t="n">
         <v>26</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX6" t="n">
         <v>23</v>
@@ -1539,7 +1606,7 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.579</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1589,10 +1656,10 @@
         <v>35.7</v>
       </c>
       <c r="J7" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L7" t="n">
         <v>7.2</v>
@@ -1601,40 +1668,40 @@
         <v>22.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.326</v>
+        <v>0.323</v>
       </c>
       <c r="O7" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P7" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.743</v>
+        <v>0.74</v>
       </c>
       <c r="R7" t="n">
         <v>10.8</v>
       </c>
       <c r="S7" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T7" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U7" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V7" t="n">
         <v>14.6</v>
       </c>
       <c r="W7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X7" t="n">
         <v>5.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z7" t="n">
         <v>19.4</v>
@@ -1643,16 +1710,16 @@
         <v>18.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.2</v>
+        <v>94</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
@@ -1661,16 +1728,16 @@
         <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,13 +1746,13 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
         <v>20</v>
@@ -1697,7 +1764,7 @@
         <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
         <v>9</v>
@@ -1709,19 +1776,19 @@
         <v>3</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
         <v>4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
         <v>24</v>
       </c>
       <c r="BB7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>14</v>
@@ -1843,25 +1910,25 @@
         <v>14</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
         <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>3</v>
@@ -1873,7 +1940,7 @@
         <v>22</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>6</v>
@@ -1885,7 +1952,7 @@
         <v>2</v>
       </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW8" t="n">
         <v>4</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -1935,103 +2002,103 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E9" t="n">
         <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>0.316</v>
+        <v>0.324</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="J9" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.426</v>
+        <v>0.427</v>
       </c>
       <c r="L9" t="n">
         <v>4.2</v>
       </c>
       <c r="M9" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.328</v>
+        <v>0.33</v>
       </c>
       <c r="O9" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P9" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.769</v>
+        <v>0.768</v>
       </c>
       <c r="R9" t="n">
         <v>12.4</v>
       </c>
       <c r="S9" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="T9" t="n">
         <v>40.2</v>
       </c>
       <c r="U9" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="V9" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W9" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
         <v>3.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>89.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-6.9</v>
+        <v>-6.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>24</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG9" t="n">
         <v>25</v>
       </c>
       <c r="AH9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI9" t="n">
         <v>27</v>
       </c>
-      <c r="AI9" t="n">
-        <v>28</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
         <v>25</v>
@@ -2043,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>12</v>
@@ -2055,7 +2122,7 @@
         <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS9" t="n">
         <v>29</v>
@@ -2067,7 +2134,7 @@
         <v>26</v>
       </c>
       <c r="AV9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
         <v>25</v>
@@ -2076,10 +2143,10 @@
         <v>30</v>
       </c>
       <c r="AY9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA9" t="n">
         <v>16</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2268,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
         <v>21</v>
@@ -2234,7 +2301,7 @@
         <v>26</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR10" t="n">
         <v>20</v>
@@ -2246,7 +2313,7 @@
         <v>27</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
         <v>8</v>
@@ -2255,7 +2322,7 @@
         <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY10" t="n">
         <v>2</v>
@@ -2270,7 +2337,7 @@
         <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>0.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>9</v>
@@ -2425,10 +2492,10 @@
         <v>19</v>
       </c>
       <c r="AT11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU11" t="n">
         <v>17</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>18</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
@@ -2437,22 +2504,22 @@
         <v>19</v>
       </c>
       <c r="AX11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.657</v>
+        <v>0.647</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,67 +2566,67 @@
         <v>34.9</v>
       </c>
       <c r="J12" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K12" t="n">
         <v>0.43</v>
       </c>
       <c r="L12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M12" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.369</v>
+        <v>0.366</v>
       </c>
       <c r="O12" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P12" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="R12" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="S12" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T12" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U12" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="V12" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W12" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y12" t="n">
         <v>6.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AA12" t="n">
         <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
@@ -2577,16 +2644,16 @@
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK12" t="n">
         <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN12" t="n">
         <v>9</v>
@@ -2607,10 +2674,10 @@
         <v>10</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
@@ -2619,13 +2686,13 @@
         <v>9</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA12" t="n">
         <v>5</v>
@@ -2634,7 +2701,7 @@
         <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>2.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AF13" t="n">
         <v>6</v>
@@ -2786,10 +2853,10 @@
         <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
         <v>12</v>
@@ -2807,7 +2874,7 @@
         <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>7</v>
@@ -2938,7 +3005,7 @@
         <v>15</v>
       </c>
       <c r="AI14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ14" t="n">
         <v>22</v>
@@ -2962,7 +3029,7 @@
         <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR14" t="n">
         <v>14</v>
@@ -2995,10 +3062,10 @@
         <v>15</v>
       </c>
       <c r="BB14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
         <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>0.595</v>
+        <v>0.583</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,37 +3112,37 @@
         <v>36.4</v>
       </c>
       <c r="J15" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="M15" t="n">
         <v>11.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.328</v>
+        <v>0.322</v>
       </c>
       <c r="O15" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P15" t="n">
         <v>23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.758</v>
+        <v>0.754</v>
       </c>
       <c r="R15" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S15" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T15" t="n">
-        <v>41.8</v>
+        <v>42.1</v>
       </c>
       <c r="U15" t="n">
         <v>19</v>
@@ -3084,46 +3151,46 @@
         <v>15.1</v>
       </c>
       <c r="W15" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="X15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF15" t="n">
         <v>9</v>
       </c>
       <c r="AG15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK15" t="n">
         <v>15</v>
@@ -3135,7 +3202,7 @@
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
@@ -3144,43 +3211,43 @@
         <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS15" t="n">
         <v>23</v>
       </c>
       <c r="AT15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU15" t="n">
         <v>24</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA15" t="n">
         <v>14</v>
       </c>
       <c r="BB15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3354,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
@@ -3338,7 +3405,7 @@
         <v>14</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV16" t="n">
         <v>18</v>
@@ -3347,7 +3414,7 @@
         <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>3</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E17" t="n">
         <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.378</v>
+        <v>0.389</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
@@ -3409,49 +3476,49 @@
         <v>36</v>
       </c>
       <c r="J17" t="n">
-        <v>85</v>
+        <v>85.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="L17" t="n">
         <v>6.6</v>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.329</v>
+        <v>0.328</v>
       </c>
       <c r="O17" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="P17" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.791</v>
+        <v>0.795</v>
       </c>
       <c r="R17" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S17" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="T17" t="n">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="U17" t="n">
         <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
         <v>4.9</v>
@@ -3460,16 +3527,16 @@
         <v>19.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AB17" t="n">
         <v>95.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>-2.7</v>
+        <v>-2.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
@@ -3481,25 +3548,25 @@
         <v>22</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
         <v>15</v>
       </c>
       <c r="AM17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
@@ -3508,7 +3575,7 @@
         <v>21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
@@ -3517,13 +3584,13 @@
         <v>28</v>
       </c>
       <c r="AT17" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AU17" t="n">
         <v>11</v>
       </c>
       <c r="AV17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AW17" t="n">
         <v>12</v>
@@ -3544,7 +3611,7 @@
         <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -3573,64 +3640,64 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.486</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
       </c>
       <c r="I18" t="n">
-        <v>35.3</v>
+        <v>35.1</v>
       </c>
       <c r="J18" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.433</v>
+        <v>0.43</v>
       </c>
       <c r="L18" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
         <v>19.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0.326</v>
+        <v>0.32</v>
       </c>
       <c r="O18" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="P18" t="n">
         <v>26.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.774</v>
+        <v>0.772</v>
       </c>
       <c r="R18" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S18" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T18" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="U18" t="n">
         <v>18.9</v>
       </c>
       <c r="V18" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W18" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X18" t="n">
         <v>4.2</v>
@@ -3639,37 +3706,37 @@
         <v>5.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>97.40000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
       </c>
       <c r="AF18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AH18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK18" t="n">
         <v>22</v>
@@ -3681,7 +3748,7 @@
         <v>13</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
         <v>5</v>
@@ -3699,7 +3766,7 @@
         <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
         <v>25</v>
@@ -3708,10 +3775,10 @@
         <v>27</v>
       </c>
       <c r="AW18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY18" t="n">
         <v>23</v>
@@ -3723,10 +3790,10 @@
         <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -3833,28 +3900,28 @@
         <v>-6.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>26</v>
       </c>
       <c r="AF19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG19" t="n">
         <v>27</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
       </c>
       <c r="AJ19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
         <v>2</v>
@@ -3887,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW19" t="n">
         <v>22</v>
@@ -3899,7 +3966,7 @@
         <v>20</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
         <v>13</v>
@@ -3908,7 +3975,7 @@
         <v>25</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
         <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>0.243</v>
+        <v>0.25</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,10 +4022,10 @@
         <v>34.5</v>
       </c>
       <c r="J20" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L20" t="n">
         <v>3.9</v>
@@ -3967,7 +4034,7 @@
         <v>12.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.315</v>
+        <v>0.314</v>
       </c>
       <c r="O20" t="n">
         <v>15.5</v>
@@ -3976,31 +4043,31 @@
         <v>20.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R20" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S20" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T20" t="n">
         <v>42.3</v>
       </c>
       <c r="U20" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V20" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W20" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X20" t="n">
         <v>4.8</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>20.7</v>
@@ -4009,13 +4076,13 @@
         <v>18.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>-5.3</v>
+        <v>-4.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,28 +4094,28 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ20" t="n">
         <v>25</v>
       </c>
       <c r="AK20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL20" t="n">
         <v>28</v>
       </c>
       <c r="AM20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AN20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>25</v>
@@ -4057,7 +4124,7 @@
         <v>17</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS20" t="n">
         <v>20</v>
@@ -4069,16 +4136,16 @@
         <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW20" t="n">
         <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ20" t="n">
         <v>22</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>1.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF21" t="n">
         <v>16</v>
@@ -4245,7 +4312,7 @@
         <v>18</v>
       </c>
       <c r="AT21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
         <v>23</v>
@@ -4272,7 +4339,7 @@
         <v>12</v>
       </c>
       <c r="BC21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -4301,85 +4368,85 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" t="n">
         <v>29</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.784</v>
+        <v>0.806</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
       <c r="J22" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.472</v>
+        <v>0.474</v>
       </c>
       <c r="L22" t="n">
         <v>6.8</v>
       </c>
       <c r="M22" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="O22" t="n">
         <v>21.8</v>
       </c>
       <c r="P22" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.795</v>
+        <v>0.794</v>
       </c>
       <c r="R22" t="n">
         <v>10.6</v>
       </c>
       <c r="S22" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T22" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="U22" t="n">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="V22" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="W22" t="n">
         <v>7.7</v>
       </c>
       <c r="X22" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.1</v>
+        <v>102.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4388,10 +4455,10 @@
         <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
         <v>10</v>
@@ -4418,7 +4485,7 @@
         <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR22" t="n">
         <v>22</v>
@@ -4427,10 +4494,10 @@
         <v>2</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -4483,85 +4550,85 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" t="n">
         <v>14</v>
       </c>
       <c r="G23" t="n">
-        <v>0.632</v>
+        <v>0.622</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
       </c>
       <c r="I23" t="n">
-        <v>34.1</v>
+        <v>33.8</v>
       </c>
       <c r="J23" t="n">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L23" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="M23" t="n">
         <v>26.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.39</v>
+        <v>0.386</v>
       </c>
       <c r="O23" t="n">
         <v>15.7</v>
       </c>
       <c r="P23" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.652</v>
+        <v>0.654</v>
       </c>
       <c r="R23" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S23" t="n">
         <v>32.3</v>
       </c>
       <c r="T23" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U23" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W23" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X23" t="n">
         <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="AA23" t="n">
         <v>20.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>5</v>
@@ -4573,16 +4640,16 @@
         <v>6</v>
       </c>
       <c r="AH23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4594,7 +4661,7 @@
         <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
@@ -4609,13 +4676,13 @@
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV23" t="n">
         <v>17</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>27</v>
@@ -4624,7 +4691,7 @@
         <v>26</v>
       </c>
       <c r="AY23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ23" t="n">
         <v>5</v>
@@ -4633,10 +4700,10 @@
         <v>10</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>7.2</v>
       </c>
       <c r="AD24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE24" t="n">
         <v>6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>7</v>
       </c>
       <c r="AF24" t="n">
         <v>9</v>
@@ -4755,7 +4822,7 @@
         <v>9</v>
       </c>
       <c r="AH24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>5</v>
@@ -4767,10 +4834,10 @@
         <v>11</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN24" t="n">
         <v>8</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-2</v>
       </c>
       <c r="AD25" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>20</v>
@@ -4949,7 +5016,7 @@
         <v>14</v>
       </c>
       <c r="AL25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM25" t="n">
         <v>14</v>
@@ -4967,13 +5034,13 @@
         <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
         <v>14</v>
       </c>
       <c r="AT25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -5029,19 +5096,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
         <v>18</v>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G26" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="H26" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I26" t="n">
         <v>37.1</v>
@@ -5050,40 +5117,40 @@
         <v>82.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L26" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M26" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O26" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P26" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R26" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S26" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="T26" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U26" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="V26" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W26" t="n">
         <v>8.699999999999999</v>
@@ -5095,34 +5162,34 @@
         <v>5.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="n">
         <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="AC26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH26" t="n">
         <v>4</v>
       </c>
-      <c r="AD26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>5</v>
-      </c>
       <c r="AI26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="n">
         <v>6</v>
@@ -5131,7 +5198,7 @@
         <v>13</v>
       </c>
       <c r="AL26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM26" t="n">
         <v>12</v>
@@ -5152,16 +5219,16 @@
         <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AU26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AW26" t="n">
         <v>5</v>
@@ -5170,10 +5237,10 @@
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
         <v>9</v>
@@ -5182,7 +5249,7 @@
         <v>5</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-7.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,13 +5368,13 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK27" t="n">
         <v>30</v>
@@ -5316,10 +5383,10 @@
         <v>17</v>
       </c>
       <c r="AM27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
@@ -5334,10 +5401,10 @@
         <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5504,7 +5571,7 @@
         <v>2</v>
       </c>
       <c r="AO28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
         <v>19</v>
@@ -5519,7 +5586,7 @@
         <v>11</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU28" t="n">
         <v>5</v>
@@ -5534,7 +5601,7 @@
         <v>25</v>
       </c>
       <c r="AY28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5546,7 +5613,7 @@
         <v>4</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>26</v>
@@ -5665,7 +5732,7 @@
         <v>26</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>26</v>
@@ -5701,13 +5768,13 @@
         <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW29" t="n">
         <v>26</v>
@@ -5716,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E30" t="n">
         <v>17</v>
       </c>
       <c r="F30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.472</v>
+        <v>0.486</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
@@ -5781,67 +5848,67 @@
         <v>0.452</v>
       </c>
       <c r="L30" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="M30" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.299</v>
+        <v>0.3</v>
       </c>
       <c r="O30" t="n">
         <v>18.5</v>
       </c>
       <c r="P30" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R30" t="n">
         <v>12.6</v>
       </c>
       <c r="S30" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T30" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="U30" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="V30" t="n">
         <v>14.2</v>
       </c>
       <c r="W30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB30" t="n">
-        <v>96.40000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE30" t="n">
         <v>19</v>
       </c>
       <c r="AF30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
         <v>19</v>
@@ -5850,7 +5917,7 @@
         <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ30" t="n">
         <v>10</v>
@@ -5862,7 +5929,7 @@
         <v>29</v>
       </c>
       <c r="AM30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN30" t="n">
         <v>30</v>
@@ -5874,19 +5941,19 @@
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
         <v>6</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV30" t="n">
         <v>7</v>
@@ -5895,13 +5962,13 @@
         <v>10</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY30" t="n">
         <v>24</v>
       </c>
       <c r="AZ30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA30" t="n">
         <v>8</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
@@ -5939,100 +6006,100 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
         <v>28</v>
       </c>
       <c r="G31" t="n">
-        <v>0.222</v>
+        <v>0.2</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J31" t="n">
-        <v>83.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M31" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0.318</v>
+        <v>0.316</v>
       </c>
       <c r="O31" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P31" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="R31" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T31" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="U31" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="V31" t="n">
         <v>15.7</v>
       </c>
       <c r="W31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X31" t="n">
         <v>7.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z31" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA31" t="n">
         <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>92.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ31" t="n">
         <v>3</v>
@@ -6044,7 +6111,7 @@
         <v>25</v>
       </c>
       <c r="AM31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN31" t="n">
         <v>24</v>
@@ -6062,16 +6129,16 @@
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AU31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW31" t="n">
         <v>11</v>
@@ -6080,13 +6147,13 @@
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ31" t="n">
         <v>27</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-3-2011-12</t>
+          <t>2012-03-03</t>
         </is>
       </c>
     </row>
